--- a/Result/profitability/9937.xlsx
+++ b/Result/profitability/9937.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.575</v>
+        <v>0.5775</v>
       </c>
       <c r="N2" t="n">
-        <v>11.95</v>
+        <v>11.90125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.52125</v>
+        <v>0.5225</v>
       </c>
       <c r="N3" t="n">
-        <v>12.1675</v>
+        <v>12.0625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4912500000000001</v>
+        <v>0.505</v>
       </c>
       <c r="N4" t="n">
-        <v>11.73875</v>
+        <v>11.61</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46875</v>
+        <v>0.47875</v>
       </c>
       <c r="N5" t="n">
-        <v>11.74875</v>
+        <v>11.615</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.445</v>
+        <v>0.4425</v>
       </c>
       <c r="N6" t="n">
-        <v>11.8775</v>
+        <v>11.70375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4075</v>
+        <v>0.41</v>
       </c>
       <c r="N7" t="n">
-        <v>11.75875</v>
+        <v>11.52375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.37625</v>
+        <v>0.37375</v>
       </c>
       <c r="N8" t="n">
-        <v>11.2</v>
+        <v>10.89625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9937</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6336</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5645</v>
+      </c>
+      <c r="E75" t="n">
+        <v>691</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="G75" t="n">
+        <v>193</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>56</v>
+      </c>
+      <c r="J75" t="n">
+        <v>249</v>
+      </c>
+      <c r="K75" t="n">
+        <v>198</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.03875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.03030303030303028</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1821589205397302</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08931552587646074</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
